--- a/Ansible to Orchestrator Transition/Ansible_to_VCF_Automation_Briefing.xlsx
+++ b/Ansible to Orchestrator Transition/Ansible_to_VCF_Automation_Briefing.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub-LocalRepos\AutomationProjects\Ansible to Orchestrator Transition\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E59CD7-0C7B-4DE2-8CFD-58E55B58CD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C1D6633AA0B3EDC0A4ABC2CE8FB32037B4C20D22" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="3270" windowWidth="44085" windowHeight="17730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -18,7 +13,12 @@
     <sheet name="By VCF Project" sheetId="3" r:id="rId3"/>
     <sheet name="Raw Data (Cleaned)" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1001,7 +1001,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1200,9 +1200,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1212,7 +1209,10 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1247,7 +1247,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
               <a:t>Top 15 Playbooks by Execution Count</a:t>
             </a:r>
           </a:p>
@@ -1257,17 +1256,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.0832738095238092E-2"/>
-          <c:y val="2.7718253968253968E-2"/>
-          <c:w val="0.67781894841269841"/>
-          <c:h val="0.84363968253968258"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -1277,11 +1266,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Playbook Prioritization'!$F$5</c:f>
+              <c:f>'Playbook Prioritization'!G5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total Runs</c:v>
+                  <c:v>Priority</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1347,61 +1336,61 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Playbook Prioritization'!$F$6:$F$20</c:f>
+              <c:f>'Playbook Prioritization'!$G$6:$G$20</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>262</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>190</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>180</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>66</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>31</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>29</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6647-4966-AAAC-43A9D50EB32A}"/>
+              <c16:uniqueId val="{00000000-3C6E-4774-BA71-6180B884DA81}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1434,20 +1423,11 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
                   <a:t>Total Runs</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.32883928571428572"/>
-              <c:y val="0.93434920634920615"/>
-            </c:manualLayout>
-          </c:layout>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1466,10 +1446,10 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorGridlines/>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1819,7 +1799,7 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="B2:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1827,25 +1807,25 @@
     <col min="7" max="7" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-    </row>
-    <row r="3" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row r="5" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:6">
+      <c r="B2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+    </row>
+    <row r="5" spans="2:6" ht="42" customHeight="1">
       <c r="B5" s="1">
         <v>158</v>
       </c>
@@ -1862,7 +1842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1879,34 +1859,34 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+    <row r="8" spans="2:6">
+      <c r="B8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-    </row>
-    <row r="9" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" spans="2:6" ht="45" customHeight="1">
+      <c r="B9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-    </row>
-    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="2:6">
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -1923,7 +1903,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6">
       <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1940,7 +1920,7 @@
         <v>0.78345323741007189</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6">
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
@@ -1957,7 +1937,7 @@
         <v>0.1366906474820144</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6">
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
@@ -1974,7 +1954,7 @@
         <v>6.1151079136690649E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6">
       <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1991,7 +1971,7 @@
         <v>1.366906474820144E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6">
       <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
@@ -2008,7 +1988,7 @@
         <v>4.3165467625899279E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6">
       <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
@@ -2025,7 +2005,7 @@
         <v>7.1942446043165469E-4</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6">
       <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
@@ -2042,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
@@ -2059,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
@@ -2076,7 +2056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
@@ -2093,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6">
       <c r="B23" s="8" t="s">
         <v>24</v>
       </c>
@@ -2129,7 +2109,7 @@
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
   <dimension ref="B2:H69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -2139,29 +2119,29 @@
     <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:8">
+      <c r="B2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-    </row>
-    <row r="5" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
@@ -2184,7 +2164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -2207,7 +2187,7 @@
         <v>0.18848920863309351</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="B7" s="5">
         <v>2</v>
       </c>
@@ -2230,7 +2210,7 @@
         <v>0.33237410071942453</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" s="5">
         <v>3</v>
       </c>
@@ -2253,7 +2233,7 @@
         <v>0.46906474820143879</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8">
       <c r="B9" s="5">
         <v>4</v>
       </c>
@@ -2276,7 +2256,7 @@
         <v>0.59856115107913666</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="B10" s="5">
         <v>5</v>
       </c>
@@ -2299,7 +2279,7 @@
         <v>0.65395683453237408</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8">
       <c r="B11" s="5">
         <v>6</v>
       </c>
@@ -2322,7 +2302,7 @@
         <v>0.70143884892086328</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8">
       <c r="B12" s="5">
         <v>7</v>
       </c>
@@ -2345,7 +2325,7 @@
         <v>0.74172661870503598</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8">
       <c r="B13" s="5">
         <v>8</v>
       </c>
@@ -2368,7 +2348,7 @@
         <v>0.77194244604316542</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8">
       <c r="B14" s="5">
         <v>9</v>
       </c>
@@ -2391,7 +2371,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8">
       <c r="B15" s="5">
         <v>10</v>
       </c>
@@ -2414,7 +2394,7 @@
         <v>0.82733812949640284</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8">
       <c r="B16" s="5">
         <v>11</v>
       </c>
@@ -2437,7 +2417,7 @@
         <v>0.85467625899280575</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8">
       <c r="B17" s="5">
         <v>12</v>
       </c>
@@ -2460,7 +2440,7 @@
         <v>0.87769784172661869</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8">
       <c r="B18" s="5">
         <v>13</v>
       </c>
@@ -2483,7 +2463,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8">
       <c r="B19" s="5">
         <v>14</v>
       </c>
@@ -2506,7 +2486,7 @@
         <v>0.92086330935251803</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8">
       <c r="B20" s="5">
         <v>15</v>
       </c>
@@ -2529,7 +2509,7 @@
         <v>0.93453237410071943</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8">
       <c r="B21" s="5">
         <v>16</v>
       </c>
@@ -2552,7 +2532,7 @@
         <v>0.94748201438848922</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8">
       <c r="B22" s="5">
         <v>17</v>
       </c>
@@ -2575,7 +2555,7 @@
         <v>0.95899280575539569</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8">
       <c r="B23" s="5">
         <v>18</v>
       </c>
@@ -2598,7 +2578,7 @@
         <v>0.96978417266187056</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8">
       <c r="B24" s="5">
         <v>19</v>
       </c>
@@ -2621,7 +2601,7 @@
         <v>0.97913669064748199</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8">
       <c r="B25" s="5">
         <v>20</v>
       </c>
@@ -2644,7 +2624,7 @@
         <v>0.9863309352517986</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8">
       <c r="B26" s="5">
         <v>21</v>
       </c>
@@ -2667,7 +2647,7 @@
         <v>0.99064748201438846</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8">
       <c r="B27" s="5">
         <v>22</v>
       </c>
@@ -2690,7 +2670,7 @@
         <v>0.99496402877697843</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8">
       <c r="B28" s="5">
         <v>23</v>
       </c>
@@ -2713,7 +2693,7 @@
         <v>0.99856115107913668</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8">
       <c r="B29" s="5">
         <v>24</v>
       </c>
@@ -2736,7 +2716,7 @@
         <v>0.99928057553956839</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8">
       <c r="B30" s="5">
         <v>25</v>
       </c>
@@ -2759,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8">
       <c r="B31" s="5">
         <v>26</v>
       </c>
@@ -2782,7 +2762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8">
       <c r="B32" s="5">
         <v>27</v>
       </c>
@@ -2805,7 +2785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8">
       <c r="B33" s="5">
         <v>28</v>
       </c>
@@ -2828,7 +2808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8">
       <c r="B34" s="5">
         <v>29</v>
       </c>
@@ -2851,7 +2831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8">
       <c r="B35" s="5">
         <v>30</v>
       </c>
@@ -2874,7 +2854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8">
       <c r="B36" s="5">
         <v>31</v>
       </c>
@@ -2897,7 +2877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8">
       <c r="B37" s="5">
         <v>32</v>
       </c>
@@ -2920,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8">
       <c r="B38" s="5">
         <v>33</v>
       </c>
@@ -2943,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8">
       <c r="B39" s="5">
         <v>34</v>
       </c>
@@ -2966,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8">
       <c r="B40" s="5">
         <v>35</v>
       </c>
@@ -2989,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8">
       <c r="B41" s="5">
         <v>36</v>
       </c>
@@ -3012,7 +2992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8">
       <c r="B42" s="5">
         <v>37</v>
       </c>
@@ -3035,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8">
       <c r="B43" s="5">
         <v>38</v>
       </c>
@@ -3058,7 +3038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8">
       <c r="B44" s="5">
         <v>39</v>
       </c>
@@ -3081,7 +3061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8">
       <c r="B45" s="5">
         <v>40</v>
       </c>
@@ -3104,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8">
       <c r="B46" s="5">
         <v>41</v>
       </c>
@@ -3127,7 +3107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8">
       <c r="B47" s="5">
         <v>42</v>
       </c>
@@ -3150,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8">
       <c r="B48" s="5">
         <v>43</v>
       </c>
@@ -3173,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8">
       <c r="B49" s="5">
         <v>44</v>
       </c>
@@ -3196,7 +3176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8">
       <c r="B50" s="5">
         <v>45</v>
       </c>
@@ -3219,7 +3199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8">
       <c r="B51" s="5">
         <v>46</v>
       </c>
@@ -3242,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8">
       <c r="B52" s="5">
         <v>47</v>
       </c>
@@ -3265,7 +3245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8">
       <c r="B53" s="5">
         <v>48</v>
       </c>
@@ -3288,7 +3268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8">
       <c r="B54" s="5">
         <v>49</v>
       </c>
@@ -3311,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8">
       <c r="B55" s="5">
         <v>50</v>
       </c>
@@ -3334,7 +3314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8">
       <c r="B56" s="5">
         <v>51</v>
       </c>
@@ -3357,7 +3337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8">
       <c r="B57" s="5">
         <v>52</v>
       </c>
@@ -3380,7 +3360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8">
       <c r="B58" s="5">
         <v>53</v>
       </c>
@@ -3403,7 +3383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8">
       <c r="B59" s="5">
         <v>54</v>
       </c>
@@ -3426,7 +3406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8">
       <c r="B60" s="5">
         <v>55</v>
       </c>
@@ -3449,7 +3429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8">
       <c r="B61" s="5">
         <v>56</v>
       </c>
@@ -3472,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8">
       <c r="B62" s="5">
         <v>57</v>
       </c>
@@ -3495,7 +3475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8">
       <c r="B63" s="5">
         <v>58</v>
       </c>
@@ -3518,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8">
       <c r="B64" s="5">
         <v>59</v>
       </c>
@@ -3541,7 +3521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8">
       <c r="B65" s="5">
         <v>60</v>
       </c>
@@ -3564,7 +3544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8">
       <c r="B66" s="5">
         <v>61</v>
       </c>
@@ -3587,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8">
       <c r="B67" s="5">
         <v>62</v>
       </c>
@@ -3610,7 +3590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8">
       <c r="B68" s="5">
         <v>63</v>
       </c>
@@ -3633,7 +3613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8">
       <c r="B69" s="5">
         <v>64</v>
       </c>
@@ -3673,7 +3653,7 @@
     <tabColor rgb="FF548235"/>
   </sheetPr>
   <dimension ref="B2:E96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -3681,23 +3661,23 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:5">
+      <c r="B2" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" s="23" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" s="17" t="s">
         <v>28</v>
       </c>
@@ -3711,7 +3691,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5">
       <c r="B6" s="12" t="s">
         <v>31</v>
       </c>
@@ -3725,7 +3705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5">
       <c r="B7" s="12" t="s">
         <v>33</v>
       </c>
@@ -3739,7 +3719,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5">
       <c r="B8" s="12" t="s">
         <v>35</v>
       </c>
@@ -3753,7 +3733,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5">
       <c r="B9" s="12" t="s">
         <v>36</v>
       </c>
@@ -3767,7 +3747,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5">
       <c r="B10" s="12" t="s">
         <v>38</v>
       </c>
@@ -3781,7 +3761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5">
       <c r="B11" s="12" t="s">
         <v>39</v>
       </c>
@@ -3795,7 +3775,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5">
       <c r="B12" s="12" t="s">
         <v>40</v>
       </c>
@@ -3809,7 +3789,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5">
       <c r="B13" s="12" t="s">
         <v>41</v>
       </c>
@@ -3823,7 +3803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5">
       <c r="B14" s="12" t="s">
         <v>42</v>
       </c>
@@ -3837,7 +3817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5">
       <c r="B15" s="12" t="s">
         <v>43</v>
       </c>
@@ -3851,7 +3831,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5">
       <c r="B16" s="12" t="s">
         <v>45</v>
       </c>
@@ -3865,7 +3845,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5">
       <c r="B17" s="12" t="s">
         <v>46</v>
       </c>
@@ -3879,7 +3859,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5">
       <c r="B18" s="12" t="s">
         <v>50</v>
       </c>
@@ -3893,7 +3873,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5">
       <c r="B19" s="12" t="s">
         <v>51</v>
       </c>
@@ -3907,7 +3887,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5">
       <c r="B20" s="12" t="s">
         <v>74</v>
       </c>
@@ -3921,7 +3901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5">
       <c r="B21" s="12" t="s">
         <v>75</v>
       </c>
@@ -3935,7 +3915,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5">
       <c r="B22" s="12" t="s">
         <v>78</v>
       </c>
@@ -3949,7 +3929,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5">
       <c r="B23" s="12" t="s">
         <v>86</v>
       </c>
@@ -3963,7 +3943,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5">
       <c r="B24" s="12" t="s">
         <v>97</v>
       </c>
@@ -3977,15 +3957,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
+    <row r="26" spans="2:5">
+      <c r="B26" s="23" t="s">
         <v>101</v>
       </c>
       <c r="C26" s="27"/>
       <c r="D26" s="27"/>
       <c r="E26" s="27"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5">
       <c r="B27" s="17" t="s">
         <v>28</v>
       </c>
@@ -3999,7 +3979,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5">
       <c r="B28" s="12" t="s">
         <v>34</v>
       </c>
@@ -4013,15 +3993,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="26" t="s">
+    <row r="30" spans="2:5">
+      <c r="B30" s="23" t="s">
         <v>102</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5">
       <c r="B31" s="17" t="s">
         <v>28</v>
       </c>
@@ -4035,7 +4015,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5">
       <c r="B32" s="12" t="s">
         <v>44</v>
       </c>
@@ -4049,7 +4029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5">
       <c r="B33" s="12" t="s">
         <v>48</v>
       </c>
@@ -4063,7 +4043,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5">
       <c r="B34" s="12" t="s">
         <v>52</v>
       </c>
@@ -4077,7 +4057,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5">
       <c r="B35" s="12" t="s">
         <v>53</v>
       </c>
@@ -4091,7 +4071,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5">
       <c r="B36" s="12" t="s">
         <v>54</v>
       </c>
@@ -4105,7 +4085,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5">
       <c r="B37" s="12" t="s">
         <v>56</v>
       </c>
@@ -4119,7 +4099,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5">
       <c r="B38" s="12" t="s">
         <v>59</v>
       </c>
@@ -4133,7 +4113,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5">
       <c r="B39" s="12" t="s">
         <v>61</v>
       </c>
@@ -4147,7 +4127,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5">
       <c r="B40" s="12" t="s">
         <v>79</v>
       </c>
@@ -4161,7 +4141,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5">
       <c r="B41" s="12" t="s">
         <v>88</v>
       </c>
@@ -4175,7 +4155,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5">
       <c r="B42" s="12" t="s">
         <v>89</v>
       </c>
@@ -4189,7 +4169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5">
       <c r="B43" s="12" t="s">
         <v>92</v>
       </c>
@@ -4203,15 +4183,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="26" t="s">
+    <row r="45" spans="2:5">
+      <c r="B45" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="27"/>
       <c r="D45" s="27"/>
       <c r="E45" s="27"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5">
       <c r="B46" s="17" t="s">
         <v>28</v>
       </c>
@@ -4225,7 +4205,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5">
       <c r="B47" s="12" t="s">
         <v>49</v>
       </c>
@@ -4239,7 +4219,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5">
       <c r="B48" s="12" t="s">
         <v>57</v>
       </c>
@@ -4253,7 +4233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5">
       <c r="B49" s="12" t="s">
         <v>63</v>
       </c>
@@ -4267,7 +4247,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5">
       <c r="B50" s="12" t="s">
         <v>73</v>
       </c>
@@ -4281,7 +4261,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5">
       <c r="B51" s="12" t="s">
         <v>82</v>
       </c>
@@ -4295,7 +4275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5">
       <c r="B52" s="12" t="s">
         <v>83</v>
       </c>
@@ -4309,7 +4289,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5">
       <c r="B53" s="12" t="s">
         <v>87</v>
       </c>
@@ -4323,7 +4303,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5">
       <c r="B54" s="12" t="s">
         <v>90</v>
       </c>
@@ -4337,7 +4317,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5">
       <c r="B55" s="12" t="s">
         <v>95</v>
       </c>
@@ -4351,7 +4331,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5">
       <c r="B56" s="12" t="s">
         <v>96</v>
       </c>
@@ -4365,15 +4345,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="26" t="s">
+    <row r="58" spans="2:5">
+      <c r="B58" s="23" t="s">
         <v>104</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
       <c r="E58" s="27"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5">
       <c r="B59" s="17" t="s">
         <v>28</v>
       </c>
@@ -4387,7 +4367,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5">
       <c r="B60" s="12" t="s">
         <v>55</v>
       </c>
@@ -4401,15 +4381,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="26" t="s">
+    <row r="62" spans="2:5">
+      <c r="B62" s="23" t="s">
         <v>105</v>
       </c>
       <c r="C62" s="27"/>
       <c r="D62" s="27"/>
       <c r="E62" s="27"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5">
       <c r="B63" s="17" t="s">
         <v>28</v>
       </c>
@@ -4423,7 +4403,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5">
       <c r="B64" s="12" t="s">
         <v>58</v>
       </c>
@@ -4437,15 +4417,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="26" t="s">
+    <row r="66" spans="2:5">
+      <c r="B66" s="23" t="s">
         <v>106</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="27"/>
       <c r="E66" s="27"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5">
       <c r="B67" s="17" t="s">
         <v>28</v>
       </c>
@@ -4459,7 +4439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5">
       <c r="B68" s="12" t="s">
         <v>62</v>
       </c>
@@ -4473,15 +4453,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="26" t="s">
+    <row r="70" spans="2:5">
+      <c r="B70" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C70" s="27"/>
       <c r="D70" s="27"/>
       <c r="E70" s="27"/>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5">
       <c r="B71" s="17" t="s">
         <v>28</v>
       </c>
@@ -4495,7 +4475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5">
       <c r="B72" s="12" t="s">
         <v>72</v>
       </c>
@@ -4509,15 +4489,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="26" t="s">
+    <row r="74" spans="2:5">
+      <c r="B74" s="23" t="s">
         <v>108</v>
       </c>
       <c r="C74" s="27"/>
       <c r="D74" s="27"/>
       <c r="E74" s="27"/>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5">
       <c r="B75" s="17" t="s">
         <v>28</v>
       </c>
@@ -4531,7 +4511,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5">
       <c r="B76" s="12" t="s">
         <v>67</v>
       </c>
@@ -4545,7 +4525,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5">
       <c r="B77" s="12" t="s">
         <v>68</v>
       </c>
@@ -4559,7 +4539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5">
       <c r="B78" s="12" t="s">
         <v>69</v>
       </c>
@@ -4573,7 +4553,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5">
       <c r="B79" s="12" t="s">
         <v>70</v>
       </c>
@@ -4587,7 +4567,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5">
       <c r="B80" s="12" t="s">
         <v>71</v>
       </c>
@@ -4601,7 +4581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5">
       <c r="B81" s="12" t="s">
         <v>80</v>
       </c>
@@ -4615,7 +4595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5">
       <c r="B82" s="12" t="s">
         <v>81</v>
       </c>
@@ -4629,7 +4609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5">
       <c r="B83" s="12" t="s">
         <v>98</v>
       </c>
@@ -4643,15 +4623,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B85" s="26" t="s">
+    <row r="85" spans="2:5">
+      <c r="B85" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C85" s="27"/>
       <c r="D85" s="27"/>
       <c r="E85" s="27"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5">
       <c r="B86" s="17" t="s">
         <v>28</v>
       </c>
@@ -4665,7 +4645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5">
       <c r="B87" s="12" t="s">
         <v>64</v>
       </c>
@@ -4679,7 +4659,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5">
       <c r="B88" s="12" t="s">
         <v>65</v>
       </c>
@@ -4693,7 +4673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5">
       <c r="B89" s="12" t="s">
         <v>66</v>
       </c>
@@ -4707,7 +4687,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5">
       <c r="B90" s="12" t="s">
         <v>76</v>
       </c>
@@ -4721,7 +4701,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5">
       <c r="B91" s="12" t="s">
         <v>77</v>
       </c>
@@ -4735,7 +4715,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5">
       <c r="B92" s="12" t="s">
         <v>84</v>
       </c>
@@ -4749,7 +4729,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5">
       <c r="B93" s="12" t="s">
         <v>85</v>
       </c>
@@ -4763,7 +4743,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:5">
       <c r="B94" s="12" t="s">
         <v>91</v>
       </c>
@@ -4777,7 +4757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5">
       <c r="B95" s="12" t="s">
         <v>93</v>
       </c>
@@ -4791,7 +4771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:5">
       <c r="B96" s="12" t="s">
         <v>94</v>
       </c>
@@ -4830,7 +4810,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="A1:G159"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4840,7 +4820,7 @@
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>110</v>
       </c>
@@ -4863,7 +4843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="19" t="s">
         <v>49</v>
       </c>
@@ -4886,7 +4866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="19" t="s">
         <v>49</v>
       </c>
@@ -4909,7 +4889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="19" t="s">
         <v>49</v>
       </c>
@@ -4932,7 +4912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="19" t="s">
         <v>78</v>
       </c>
@@ -4955,7 +4935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="19" t="s">
         <v>78</v>
       </c>
@@ -4978,7 +4958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="19" t="s">
         <v>78</v>
       </c>
@@ -5001,7 +4981,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="19" t="s">
         <v>41</v>
       </c>
@@ -5024,7 +5004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="19" t="s">
         <v>41</v>
       </c>
@@ -5047,7 +5027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="19" t="s">
         <v>41</v>
       </c>
@@ -5070,7 +5050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="19" t="s">
         <v>77</v>
       </c>
@@ -5093,7 +5073,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="19" t="s">
         <v>62</v>
       </c>
@@ -5116,7 +5096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="19" t="s">
         <v>62</v>
       </c>
@@ -5139,7 +5119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="19" t="s">
         <v>56</v>
       </c>
@@ -5162,7 +5142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="19" t="s">
         <v>56</v>
       </c>
@@ -5185,7 +5165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="19" t="s">
         <v>56</v>
       </c>
@@ -5208,7 +5188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="19" t="s">
         <v>56</v>
       </c>
@@ -5231,7 +5211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="19" t="s">
         <v>56</v>
       </c>
@@ -5254,7 +5234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="19" t="s">
         <v>56</v>
       </c>
@@ -5277,7 +5257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="19" t="s">
         <v>61</v>
       </c>
@@ -5300,7 +5280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="19" t="s">
         <v>61</v>
       </c>
@@ -5323,7 +5303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="19" t="s">
         <v>59</v>
       </c>
@@ -5346,7 +5326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="19" t="s">
         <v>59</v>
       </c>
@@ -5369,7 +5349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="19" t="s">
         <v>59</v>
       </c>
@@ -5392,7 +5372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="19" t="s">
         <v>44</v>
       </c>
@@ -5415,7 +5395,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="19" t="s">
         <v>44</v>
       </c>
@@ -5438,7 +5418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="19" t="s">
         <v>44</v>
       </c>
@@ -5461,7 +5441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="19" t="s">
         <v>44</v>
       </c>
@@ -5484,7 +5464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="19" t="s">
         <v>44</v>
       </c>
@@ -5507,7 +5487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="19" t="s">
         <v>44</v>
       </c>
@@ -5530,7 +5510,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="19" t="s">
         <v>63</v>
       </c>
@@ -5553,7 +5533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="19" t="s">
         <v>54</v>
       </c>
@@ -5576,7 +5556,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="19" t="s">
         <v>54</v>
       </c>
@@ -5599,7 +5579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="19" t="s">
         <v>73</v>
       </c>
@@ -5622,7 +5602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="19" t="s">
         <v>72</v>
       </c>
@@ -5645,7 +5625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="19" t="s">
         <v>72</v>
       </c>
@@ -5668,7 +5648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="19" t="s">
         <v>72</v>
       </c>
@@ -5691,7 +5671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="19" t="s">
         <v>72</v>
       </c>
@@ -5714,7 +5694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="19" t="s">
         <v>50</v>
       </c>
@@ -5737,7 +5717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="19" t="s">
         <v>50</v>
       </c>
@@ -5760,7 +5740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="19" t="s">
         <v>74</v>
       </c>
@@ -5783,7 +5763,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="19" t="s">
         <v>43</v>
       </c>
@@ -5806,7 +5786,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="19" t="s">
         <v>31</v>
       </c>
@@ -5829,7 +5809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="19" t="s">
         <v>31</v>
       </c>
@@ -5852,7 +5832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="19" t="s">
         <v>31</v>
       </c>
@@ -5875,7 +5855,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="19" t="s">
         <v>31</v>
       </c>
@@ -5898,7 +5878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="19" t="s">
         <v>31</v>
       </c>
@@ -5921,7 +5901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" s="19" t="s">
         <v>42</v>
       </c>
@@ -5944,7 +5924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="19" t="s">
         <v>39</v>
       </c>
@@ -5967,7 +5947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="19" t="s">
         <v>71</v>
       </c>
@@ -5990,7 +5970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="19" t="s">
         <v>69</v>
       </c>
@@ -6013,7 +5993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="19" t="s">
         <v>70</v>
       </c>
@@ -6036,7 +6016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="19" t="s">
         <v>68</v>
       </c>
@@ -6059,7 +6039,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="19" t="s">
         <v>58</v>
       </c>
@@ -6082,7 +6062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="19" t="s">
         <v>58</v>
       </c>
@@ -6105,7 +6085,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="19" t="s">
         <v>58</v>
       </c>
@@ -6128,7 +6108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="19" t="s">
         <v>58</v>
       </c>
@@ -6151,7 +6131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="19" t="s">
         <v>46</v>
       </c>
@@ -6174,7 +6154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="19" t="s">
         <v>67</v>
       </c>
@@ -6197,7 +6177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="19" t="s">
         <v>82</v>
       </c>
@@ -6220,7 +6200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="19" t="s">
         <v>82</v>
       </c>
@@ -6243,7 +6223,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="19" t="s">
         <v>80</v>
       </c>
@@ -6266,7 +6246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="19" t="s">
         <v>81</v>
       </c>
@@ -6289,7 +6269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="19" t="s">
         <v>38</v>
       </c>
@@ -6312,7 +6292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="19" t="s">
         <v>38</v>
       </c>
@@ -6335,7 +6315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="19" t="s">
         <v>89</v>
       </c>
@@ -6358,7 +6338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="19" t="s">
         <v>89</v>
       </c>
@@ -6381,7 +6361,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="19" t="s">
         <v>52</v>
       </c>
@@ -6404,7 +6384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="19" t="s">
         <v>52</v>
       </c>
@@ -6427,7 +6407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="19" t="s">
         <v>79</v>
       </c>
@@ -6450,7 +6430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="19" t="s">
         <v>48</v>
       </c>
@@ -6473,7 +6453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="19" t="s">
         <v>48</v>
       </c>
@@ -6496,7 +6476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="19" t="s">
         <v>48</v>
       </c>
@@ -6519,7 +6499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="19" t="s">
         <v>48</v>
       </c>
@@ -6542,7 +6522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="19" t="s">
         <v>48</v>
       </c>
@@ -6565,7 +6545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="19" t="s">
         <v>48</v>
       </c>
@@ -6588,7 +6568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="19" t="s">
         <v>48</v>
       </c>
@@ -6611,7 +6591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="19" t="s">
         <v>48</v>
       </c>
@@ -6634,7 +6614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="19" t="s">
         <v>88</v>
       </c>
@@ -6657,7 +6637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="19" t="s">
         <v>88</v>
       </c>
@@ -6680,7 +6660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="19" t="s">
         <v>88</v>
       </c>
@@ -6703,7 +6683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="19" t="s">
         <v>53</v>
       </c>
@@ -6726,7 +6706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="19" t="s">
         <v>53</v>
       </c>
@@ -6749,7 +6729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="19" t="s">
         <v>53</v>
       </c>
@@ -6772,7 +6752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="19" t="s">
         <v>53</v>
       </c>
@@ -6795,7 +6775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="19" t="s">
         <v>53</v>
       </c>
@@ -6818,7 +6798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="19" t="s">
         <v>57</v>
       </c>
@@ -6841,7 +6821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="19" t="s">
         <v>57</v>
       </c>
@@ -6864,7 +6844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="19" t="s">
         <v>57</v>
       </c>
@@ -6887,7 +6867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="19" t="s">
         <v>57</v>
       </c>
@@ -6910,7 +6890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="19" t="s">
         <v>87</v>
       </c>
@@ -6933,7 +6913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="19" t="s">
         <v>87</v>
       </c>
@@ -6956,7 +6936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="19" t="s">
         <v>87</v>
       </c>
@@ -6979,7 +6959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="19" t="s">
         <v>66</v>
       </c>
@@ -7002,7 +6982,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="19" t="s">
         <v>76</v>
       </c>
@@ -7025,7 +7005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="19" t="s">
         <v>64</v>
       </c>
@@ -7048,7 +7028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97" s="19" t="s">
         <v>86</v>
       </c>
@@ -7071,7 +7051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="19" t="s">
         <v>83</v>
       </c>
@@ -7094,7 +7074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99" s="19" t="s">
         <v>85</v>
       </c>
@@ -7117,7 +7097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100" s="19" t="s">
         <v>84</v>
       </c>
@@ -7140,7 +7120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="19" t="s">
         <v>36</v>
       </c>
@@ -7163,7 +7143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="19" t="s">
         <v>36</v>
       </c>
@@ -7186,7 +7166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103" s="19" t="s">
         <v>36</v>
       </c>
@@ -7209,7 +7189,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104" s="19" t="s">
         <v>36</v>
       </c>
@@ -7232,7 +7212,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="19" t="s">
         <v>36</v>
       </c>
@@ -7255,7 +7235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106" s="19" t="s">
         <v>36</v>
       </c>
@@ -7278,7 +7258,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107" s="19" t="s">
         <v>36</v>
       </c>
@@ -7301,7 +7281,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108" s="19" t="s">
         <v>36</v>
       </c>
@@ -7324,7 +7304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109" s="19" t="s">
         <v>40</v>
       </c>
@@ -7347,7 +7327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110" s="19" t="s">
         <v>40</v>
       </c>
@@ -7370,7 +7350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111" s="19" t="s">
         <v>40</v>
       </c>
@@ -7393,7 +7373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112" s="19" t="s">
         <v>33</v>
       </c>
@@ -7416,7 +7396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113" s="19" t="s">
         <v>33</v>
       </c>
@@ -7439,7 +7419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="19" t="s">
         <v>33</v>
       </c>
@@ -7462,7 +7442,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115" s="19" t="s">
         <v>33</v>
       </c>
@@ -7485,7 +7465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="19" t="s">
         <v>33</v>
       </c>
@@ -7508,7 +7488,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117" s="19" t="s">
         <v>33</v>
       </c>
@@ -7531,7 +7511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="19" t="s">
         <v>33</v>
       </c>
@@ -7554,7 +7534,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119" s="19" t="s">
         <v>33</v>
       </c>
@@ -7577,7 +7557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120" s="19" t="s">
         <v>33</v>
       </c>
@@ -7600,7 +7580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121" s="19" t="s">
         <v>33</v>
       </c>
@@ -7623,7 +7603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="19" t="s">
         <v>35</v>
       </c>
@@ -7646,7 +7626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -7669,7 +7649,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="19" t="s">
         <v>35</v>
       </c>
@@ -7692,7 +7672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="19" t="s">
         <v>35</v>
       </c>
@@ -7715,7 +7695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="19" t="s">
         <v>35</v>
       </c>
@@ -7738,7 +7718,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127" s="19" t="s">
         <v>45</v>
       </c>
@@ -7761,7 +7741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7">
       <c r="A128" s="19" t="s">
         <v>45</v>
       </c>
@@ -7784,7 +7764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7">
       <c r="A129" s="19" t="s">
         <v>45</v>
       </c>
@@ -7807,7 +7787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7">
       <c r="A130" s="19" t="s">
         <v>90</v>
       </c>
@@ -7830,7 +7810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7">
       <c r="A131" s="19" t="s">
         <v>90</v>
       </c>
@@ -7853,7 +7833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132" s="19" t="s">
         <v>92</v>
       </c>
@@ -7876,7 +7856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7">
       <c r="A133" s="19" t="s">
         <v>92</v>
       </c>
@@ -7899,7 +7879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -7922,7 +7902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7">
       <c r="A135" s="19" t="s">
         <v>65</v>
       </c>
@@ -7945,7 +7925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7">
       <c r="A136" s="19" t="s">
         <v>65</v>
       </c>
@@ -7968,7 +7948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7">
       <c r="A137" s="19" t="s">
         <v>91</v>
       </c>
@@ -7991,7 +7971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138" s="19" t="s">
         <v>93</v>
       </c>
@@ -8014,7 +7994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7">
       <c r="A139" s="19" t="s">
         <v>93</v>
       </c>
@@ -8037,7 +8017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7">
       <c r="A140" s="19" t="s">
         <v>94</v>
       </c>
@@ -8060,7 +8040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7">
       <c r="A141" s="19" t="s">
         <v>75</v>
       </c>
@@ -8083,7 +8063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7">
       <c r="A142" s="19" t="s">
         <v>75</v>
       </c>
@@ -8106,7 +8086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143" s="19" t="s">
         <v>75</v>
       </c>
@@ -8129,7 +8109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144" s="19" t="s">
         <v>75</v>
       </c>
@@ -8152,7 +8132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7">
       <c r="A145" s="19" t="s">
         <v>75</v>
       </c>
@@ -8175,7 +8155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7">
       <c r="A146" s="19" t="s">
         <v>95</v>
       </c>
@@ -8198,7 +8178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7">
       <c r="A147" s="19" t="s">
         <v>95</v>
       </c>
@@ -8221,7 +8201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7">
       <c r="A148" s="19" t="s">
         <v>95</v>
       </c>
@@ -8244,7 +8224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7">
       <c r="A149" s="19" t="s">
         <v>96</v>
       </c>
@@ -8267,7 +8247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7">
       <c r="A150" s="19" t="s">
         <v>34</v>
       </c>
@@ -8290,7 +8270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151" s="19" t="s">
         <v>34</v>
       </c>
@@ -8313,7 +8293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7">
       <c r="A152" s="19" t="s">
         <v>34</v>
       </c>
@@ -8336,7 +8316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7">
       <c r="A153" s="19" t="s">
         <v>34</v>
       </c>
@@ -8359,7 +8339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7">
       <c r="A154" s="19" t="s">
         <v>34</v>
       </c>
@@ -8382,7 +8362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7">
       <c r="A155" s="19" t="s">
         <v>34</v>
       </c>
@@ -8405,7 +8385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7">
       <c r="A156" s="19" t="s">
         <v>51</v>
       </c>
@@ -8428,7 +8408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7">
       <c r="A157" s="19" t="s">
         <v>97</v>
       </c>
@@ -8451,7 +8431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7">
       <c r="A158" s="19" t="s">
         <v>55</v>
       </c>
@@ -8472,7 +8452,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7">
       <c r="A159" s="19" t="s">
         <v>98</v>
       </c>
@@ -8499,4 +8479,193 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F31F3E2BDF57D84FBD1940DB5BFE70A1" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a9b561b9de271dadfdbb55af4b004760">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="214119f6-a8cf-4ab0-bc74-24d72ad44cda" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d4541ef4acfa0f2fee95c92c0176a78" ns2:_="">
+    <xsd:import namespace="214119f6-a8cf-4ab0-bc74-24d72ad44cda"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="214119f6-a8cf-4ab0-bc74-24d72ad44cda" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A3CDFF-0EB2-454B-9F84-0711B7F2FCA8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82BE0BA-E49D-4DD5-864B-B261E6E5392C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E23F133A-2824-4EC8-8E93-A4782297027B}"/>
 </file>